--- a/layout/CATALOGOS/Tipo Tasa.xlsx
+++ b/layout/CATALOGOS/Tipo Tasa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fsaavedra/Documents/IFRS-REG_UPDATE/LAYOUTS/CREDITO/CATALOGOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\CATALOGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{691E7D67-E004-4945-BE07-05B76CA98D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AF5335-868D-43BE-B0D3-9BF28B90EFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1500" windowWidth="23340" windowHeight="13900" xr2:uid="{DA0D3342-A247-8E45-8D2A-8D535FE0A384}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="29190" windowHeight="11220" xr2:uid="{DA0D3342-A247-8E45-8D2A-8D535FE0A384}"/>
   </bookViews>
   <sheets>
     <sheet name="Tipo Tasa" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Tasa Fija</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Descripcion</t>
-  </si>
-  <si>
-    <t>Tipo Tasa</t>
   </si>
 </sst>
 </file>
@@ -128,9 +125,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -168,7 +165,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -274,7 +271,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -416,7 +413,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -424,43 +421,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA977E0-AC75-7944-BC1D-2680DE9D3E66}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.5">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -470,6 +462,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f630fe88fca46f474c1a040348173530">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43503493d423bb6dbf2c83667b0fea1b" ns2:_="" ns3:_="">
     <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
@@ -670,34 +682,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8046F75E-50C4-4E6E-AB6A-8F029E0053E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51186604-174F-4FFD-A8C4-58A2F19A61E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDAAF8D-8C2B-4E11-BE7C-F1672165DAA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDAAF8D-8C2B-4E11-BE7C-F1672165DAA5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51186604-174F-4FFD-A8C4-58A2F19A61E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8046F75E-50C4-4E6E-AB6A-8F029E0053E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>